--- a/Data_clean/MCAS/Estados_US/Edos_USA_2017/VERMONT_2017.xlsx
+++ b/Data_clean/MCAS/Estados_US/Edos_USA_2017/VERMONT_2017.xlsx
@@ -351,28 +351,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D480"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
@@ -384,7 +384,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Comitán de Domínguez</t>
+          <t>Comitán De Domínguez</t>
         </is>
       </c>
       <c r="C2">
@@ -395,6 +395,11 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>Escuintla</t>
@@ -408,6 +413,11 @@
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>Las Margaritas</t>
@@ -421,6 +431,11 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>Las Rosas</t>
@@ -434,9 +449,14 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mazapa de Madero</t>
+          <t>Mazapa De Madero</t>
         </is>
       </c>
       <c r="C6">
@@ -447,6 +467,11 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>Tecpatán</t>
@@ -460,6 +485,11 @@
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>Total</t>
@@ -491,6 +521,11 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>Total</t>
@@ -522,6 +557,11 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>Total</t>
@@ -553,6 +593,11 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>Total</t>
@@ -573,7 +618,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Miahuatlán de Porfirio Díaz</t>
+          <t>Miahuatlán De Porfirio Díaz</t>
         </is>
       </c>
       <c r="C15">
@@ -584,6 +629,11 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>San Antonino Monte Verde</t>
@@ -597,6 +647,11 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>San Juan Teposcolula</t>
@@ -610,6 +665,11 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>Total</t>
@@ -641,6 +701,11 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>Hueytamalco</t>
@@ -654,6 +719,11 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>Jolalpan</t>
@@ -667,9 +737,14 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tecali de Herrera</t>
+          <t>Tecali De Herrera</t>
         </is>
       </c>
       <c r="C22">
@@ -680,6 +755,11 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>Xiutetelco</t>
@@ -693,6 +773,11 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>Total</t>
@@ -724,6 +809,11 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>Total</t>
@@ -755,6 +845,11 @@
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>Huimanguillo</t>
@@ -768,6 +863,11 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>Total</t>
@@ -799,6 +899,11 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>Total</t>
@@ -830,6 +935,11 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>Atzalan</t>
@@ -843,6 +953,11 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>Las Choapas</t>
@@ -856,9 +971,14 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Martínez de la Torre</t>
+          <t>Martínez De La Torre</t>
         </is>
       </c>
       <c r="C35">
@@ -869,6 +989,11 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>Misantla</t>
@@ -882,6 +1007,11 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
           <t>Playa Vicente</t>
@@ -895,6 +1025,11 @@
       </c>
     </row>
     <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
           <t>Tatatila</t>
@@ -908,6 +1043,11 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>Veracruz</t>
@@ -921,6 +1061,11 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>Xalapa</t>
@@ -934,6 +1079,11 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>Total</t>
@@ -957,76 +1107,6 @@
       </c>
       <c r="D42">
         <v>1</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 826,856</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Junio de 2018</t>
-        </is>
-      </c>
-    </row>
-    <row r="476">
-      <c r="A476" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 1,114,005</t>
-        </is>
-      </c>
-    </row>
-    <row r="477">
-      <c r="A477" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="478">
-      <c r="A478" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="479">
-      <c r="A479" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="480">
-      <c r="A480" t="inlineStr">
-        <is>
-          <t>Junio de 2016</t>
-        </is>
       </c>
     </row>
   </sheetData>
